--- a/output/graficos_educacion_tasas/comunal_e_rezjov_a_2021_aysen.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezjov_a_2021_aysen.xlsx
@@ -60,7 +60,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:38</t>
+    <t xml:space="preserve">2026-09-09 20:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_rezjov_a_2021_aysen.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezjov_a_2021_aysen.xlsx
@@ -24,33 +24,33 @@
     <t xml:space="preserve">Valor (%)</t>
   </si>
   <si>
+    <t xml:space="preserve">Coyhaique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lago Verde</t>
+  </si>
+  <si>
     <t xml:space="preserve">Aysén</t>
   </si>
   <si>
+    <t xml:space="preserve">Cisnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guaitecas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cochrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tortel</t>
+  </si>
+  <si>
     <t xml:space="preserve">Chile Chico</t>
   </si>
   <si>
-    <t xml:space="preserve">Cisnes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cochrane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coyhaique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guaitecas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lago Verde</t>
-  </si>
-  <si>
     <t xml:space="preserve">Río Ibáñez</t>
   </si>
   <si>
-    <t xml:space="preserve">Tortel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -60,7 +60,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:41</t>
+    <t xml:space="preserve">2026-09-18 10:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -472,7 +472,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>5.23</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="3">
@@ -480,7 +480,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>5.61</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="4">
@@ -488,7 +488,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4.52</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="5">
@@ -496,7 +496,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4.05</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="6">
@@ -504,7 +504,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>4.32</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="7">
@@ -512,7 +512,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>2.86</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="8">
@@ -520,7 +520,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>2.94</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="9">
@@ -528,7 +528,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>2.78</v>
+        <v>5.61</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>3.31</v>
+        <v>2.78</v>
       </c>
     </row>
   </sheetData>
